--- a/artfynd/A 1582-2025 artfynd.xlsx
+++ b/artfynd/A 1582-2025 artfynd.xlsx
@@ -6782,7 +6782,7 @@
         <v>135187673</v>
       </c>
       <c r="B59" t="n">
-        <v>57153</v>
+        <v>57162</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6790,21 +6790,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>102612</v>
+        <v>100138</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>

--- a/artfynd/A 1582-2025 artfynd.xlsx
+++ b/artfynd/A 1582-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY85"/>
+  <dimension ref="A1:AZ85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135187604</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135187631</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135187653</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135187656</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135187669</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1314,6 +1344,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135187620</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1421,6 +1456,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135187617</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1528,6 +1568,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135187648</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1635,6 +1680,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135187662</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1742,6 +1792,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135187668</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1854,6 +1909,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135187637</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1961,6 +2021,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135187635</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2068,6 +2133,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135187640</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2175,6 +2245,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135187643</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2282,6 +2357,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135187591</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2389,6 +2469,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135187586</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2496,6 +2581,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135187590</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2603,6 +2693,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135187592</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2710,6 +2805,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135187600</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2817,6 +2917,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135187605</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2924,6 +3029,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135187628</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3031,6 +3141,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135187630</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3138,6 +3253,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135187632</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3245,6 +3365,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135187633</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3352,6 +3477,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135187638</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3459,6 +3589,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135187644</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3566,6 +3701,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135187650</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3673,6 +3813,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135187651</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3780,6 +3925,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135187659</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3887,6 +4037,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135187661</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3994,6 +4149,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135187663</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4101,6 +4261,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135187664</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4208,6 +4373,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135187672</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4315,6 +4485,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135187675</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4422,6 +4597,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135187679</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4529,6 +4709,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135187589</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4636,6 +4821,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135187629</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4743,6 +4933,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135187616</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4850,6 +5045,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135187641</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4957,6 +5157,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135187613</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5064,6 +5269,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135187615</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5171,6 +5381,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135187606</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5278,6 +5493,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135187607</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5385,6 +5605,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135187610</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5492,6 +5717,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135187611</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5599,6 +5829,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135187619</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5706,6 +5941,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135187621</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5813,6 +6053,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135187622</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5920,6 +6165,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135187624</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6027,6 +6277,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135187626</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6134,6 +6389,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135187647</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6241,6 +6501,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135187677</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6348,6 +6613,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135187618</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6455,6 +6725,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135187596</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6562,6 +6837,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135187598</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6669,6 +6949,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135187678</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6776,6 +7061,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135187646</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6896,6 +7186,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135187673</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7015,6 +7310,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135187657</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7130,6 +7430,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135187674</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7249,6 +7554,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135187660</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7368,6 +7678,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135187665</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7480,6 +7795,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135187595</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7592,6 +7912,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135187602</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7704,6 +8029,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135187603</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7816,6 +8146,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135187623</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7928,6 +8263,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135187645</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8040,6 +8380,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135187649</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8152,6 +8497,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135187654</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8264,6 +8614,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135187655</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8376,6 +8731,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135187658</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8493,6 +8853,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135187666</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8605,6 +8970,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135187670</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8717,6 +9087,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135187671</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8824,6 +9199,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135187588</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8931,6 +9311,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135187614</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -9038,6 +9423,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135187642</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9145,6 +9535,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135187676</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9252,6 +9647,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135187593</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9359,6 +9759,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135187601</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9466,6 +9871,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135187608</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9573,6 +9983,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135187625</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9680,6 +10095,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135187627</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9787,8 +10207,99 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135187652</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 1582-2025 artfynd.xlsx
+++ b/artfynd/A 1582-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135187604</v>
       </c>
       <c r="B2" t="n">
-        <v>97435</v>
+        <v>97479</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135187631</v>
       </c>
       <c r="B3" t="n">
-        <v>97435</v>
+        <v>97479</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135187653</v>
       </c>
       <c r="B4" t="n">
-        <v>97435</v>
+        <v>97479</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135187656</v>
       </c>
       <c r="B5" t="n">
-        <v>97435</v>
+        <v>97479</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135187669</v>
       </c>
       <c r="B6" t="n">
-        <v>97435</v>
+        <v>97479</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135187620</v>
       </c>
       <c r="B7" t="n">
-        <v>79405</v>
+        <v>79443</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>135187617</v>
       </c>
       <c r="B8" t="n">
-        <v>83350</v>
+        <v>83390</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>135187648</v>
       </c>
       <c r="B9" t="n">
-        <v>83350</v>
+        <v>83390</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>135187662</v>
       </c>
       <c r="B10" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>135187668</v>
       </c>
       <c r="B11" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>135187637</v>
       </c>
       <c r="B12" t="n">
-        <v>91988</v>
+        <v>92030</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>135187635</v>
       </c>
       <c r="B13" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>135187640</v>
       </c>
       <c r="B14" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>135187643</v>
       </c>
       <c r="B15" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>135187591</v>
       </c>
       <c r="B16" t="n">
-        <v>91937</v>
+        <v>91979</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
         <v>135187586</v>
       </c>
       <c r="B17" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2480,7 +2480,7 @@
         <v>135187590</v>
       </c>
       <c r="B18" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>135187592</v>
       </c>
       <c r="B19" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2704,7 +2704,7 @@
         <v>135187600</v>
       </c>
       <c r="B20" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
         <v>135187605</v>
       </c>
       <c r="B21" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2928,7 +2928,7 @@
         <v>135187628</v>
       </c>
       <c r="B22" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
         <v>135187630</v>
       </c>
       <c r="B23" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         <v>135187632</v>
       </c>
       <c r="B24" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3264,7 +3264,7 @@
         <v>135187633</v>
       </c>
       <c r="B25" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3376,7 +3376,7 @@
         <v>135187638</v>
       </c>
       <c r="B26" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3488,7 +3488,7 @@
         <v>135187644</v>
       </c>
       <c r="B27" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3600,7 +3600,7 @@
         <v>135187650</v>
       </c>
       <c r="B28" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3712,7 +3712,7 @@
         <v>135187651</v>
       </c>
       <c r="B29" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3824,7 +3824,7 @@
         <v>135187659</v>
       </c>
       <c r="B30" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3936,7 +3936,7 @@
         <v>135187661</v>
       </c>
       <c r="B31" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4048,7 +4048,7 @@
         <v>135187663</v>
       </c>
       <c r="B32" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4160,7 +4160,7 @@
         <v>135187664</v>
       </c>
       <c r="B33" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
         <v>135187672</v>
       </c>
       <c r="B34" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4384,7 +4384,7 @@
         <v>135187675</v>
       </c>
       <c r="B35" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4496,7 +4496,7 @@
         <v>135187679</v>
       </c>
       <c r="B36" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4608,7 +4608,7 @@
         <v>135187589</v>
       </c>
       <c r="B37" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4720,7 +4720,7 @@
         <v>135187629</v>
       </c>
       <c r="B38" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4832,7 +4832,7 @@
         <v>135187616</v>
       </c>
       <c r="B39" t="n">
-        <v>79130</v>
+        <v>79168</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4944,7 +4944,7 @@
         <v>135187641</v>
       </c>
       <c r="B40" t="n">
-        <v>79130</v>
+        <v>79168</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5056,7 +5056,7 @@
         <v>135187613</v>
       </c>
       <c r="B41" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5168,7 +5168,7 @@
         <v>135187615</v>
       </c>
       <c r="B42" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5280,7 +5280,7 @@
         <v>135187606</v>
       </c>
       <c r="B43" t="n">
-        <v>80488</v>
+        <v>80526</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5392,7 +5392,7 @@
         <v>135187607</v>
       </c>
       <c r="B44" t="n">
-        <v>80488</v>
+        <v>80526</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5504,7 +5504,7 @@
         <v>135187610</v>
       </c>
       <c r="B45" t="n">
-        <v>80488</v>
+        <v>80526</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5616,7 +5616,7 @@
         <v>135187611</v>
       </c>
       <c r="B46" t="n">
-        <v>80488</v>
+        <v>80526</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5728,7 +5728,7 @@
         <v>135187619</v>
       </c>
       <c r="B47" t="n">
-        <v>80488</v>
+        <v>80526</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5840,7 +5840,7 @@
         <v>135187621</v>
       </c>
       <c r="B48" t="n">
-        <v>80488</v>
+        <v>80526</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5952,7 +5952,7 @@
         <v>135187622</v>
       </c>
       <c r="B49" t="n">
-        <v>80488</v>
+        <v>80526</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6064,7 +6064,7 @@
         <v>135187624</v>
       </c>
       <c r="B50" t="n">
-        <v>80488</v>
+        <v>80526</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6176,7 +6176,7 @@
         <v>135187626</v>
       </c>
       <c r="B51" t="n">
-        <v>80488</v>
+        <v>80526</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6288,7 +6288,7 @@
         <v>135187647</v>
       </c>
       <c r="B52" t="n">
-        <v>80488</v>
+        <v>80526</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6400,7 +6400,7 @@
         <v>135187677</v>
       </c>
       <c r="B53" t="n">
-        <v>80488</v>
+        <v>80526</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6512,7 +6512,7 @@
         <v>135187618</v>
       </c>
       <c r="B54" t="n">
-        <v>80492</v>
+        <v>80530</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6624,7 +6624,7 @@
         <v>135187596</v>
       </c>
       <c r="B55" t="n">
-        <v>80499</v>
+        <v>80537</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6736,7 +6736,7 @@
         <v>135187598</v>
       </c>
       <c r="B56" t="n">
-        <v>80499</v>
+        <v>80537</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6848,7 +6848,7 @@
         <v>135187678</v>
       </c>
       <c r="B57" t="n">
-        <v>80499</v>
+        <v>80537</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6960,7 +6960,7 @@
         <v>135187646</v>
       </c>
       <c r="B58" t="n">
-        <v>80500</v>
+        <v>80538</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7072,7 +7072,7 @@
         <v>135187673</v>
       </c>
       <c r="B59" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7197,7 +7197,7 @@
         <v>135187657</v>
       </c>
       <c r="B60" t="n">
-        <v>57796</v>
+        <v>57801</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7321,7 +7321,7 @@
         <v>135187674</v>
       </c>
       <c r="B61" t="n">
-        <v>57796</v>
+        <v>57801</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7441,7 +7441,7 @@
         <v>135187660</v>
       </c>
       <c r="B62" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7565,7 +7565,7 @@
         <v>135187665</v>
       </c>
       <c r="B63" t="n">
-        <v>58131</v>
+        <v>58136</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7689,7 +7689,7 @@
         <v>135187595</v>
       </c>
       <c r="B64" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7806,7 +7806,7 @@
         <v>135187602</v>
       </c>
       <c r="B65" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7923,7 +7923,7 @@
         <v>135187603</v>
       </c>
       <c r="B66" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8040,7 +8040,7 @@
         <v>135187623</v>
       </c>
       <c r="B67" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8157,7 +8157,7 @@
         <v>135187645</v>
       </c>
       <c r="B68" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8274,7 +8274,7 @@
         <v>135187649</v>
       </c>
       <c r="B69" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8391,7 +8391,7 @@
         <v>135187654</v>
       </c>
       <c r="B70" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8508,7 +8508,7 @@
         <v>135187655</v>
       </c>
       <c r="B71" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8625,7 +8625,7 @@
         <v>135187658</v>
       </c>
       <c r="B72" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8742,7 +8742,7 @@
         <v>135187666</v>
       </c>
       <c r="B73" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8864,7 +8864,7 @@
         <v>135187670</v>
       </c>
       <c r="B74" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8981,7 +8981,7 @@
         <v>135187671</v>
       </c>
       <c r="B75" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9098,7 +9098,7 @@
         <v>135187588</v>
       </c>
       <c r="B76" t="n">
-        <v>79131</v>
+        <v>79169</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9210,7 +9210,7 @@
         <v>135187614</v>
       </c>
       <c r="B77" t="n">
-        <v>79131</v>
+        <v>79169</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9322,7 +9322,7 @@
         <v>135187642</v>
       </c>
       <c r="B78" t="n">
-        <v>79131</v>
+        <v>79169</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9434,7 +9434,7 @@
         <v>135187676</v>
       </c>
       <c r="B79" t="n">
-        <v>79131</v>
+        <v>79169</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9546,7 +9546,7 @@
         <v>135187593</v>
       </c>
       <c r="B80" t="n">
-        <v>80438</v>
+        <v>80476</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9658,7 +9658,7 @@
         <v>135187601</v>
       </c>
       <c r="B81" t="n">
-        <v>80438</v>
+        <v>80476</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9770,7 +9770,7 @@
         <v>135187608</v>
       </c>
       <c r="B82" t="n">
-        <v>80438</v>
+        <v>80476</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9882,7 +9882,7 @@
         <v>135187625</v>
       </c>
       <c r="B83" t="n">
-        <v>80438</v>
+        <v>80476</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9994,7 +9994,7 @@
         <v>135187627</v>
       </c>
       <c r="B84" t="n">
-        <v>80438</v>
+        <v>80476</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10106,7 +10106,7 @@
         <v>135187652</v>
       </c>
       <c r="B85" t="n">
-        <v>80438</v>
+        <v>80476</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>

--- a/artfynd/A 1582-2025 artfynd.xlsx
+++ b/artfynd/A 1582-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135187604</v>
       </c>
       <c r="B2" t="n">
-        <v>97479</v>
+        <v>97506</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135187631</v>
       </c>
       <c r="B3" t="n">
-        <v>97479</v>
+        <v>97506</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135187653</v>
       </c>
       <c r="B4" t="n">
-        <v>97479</v>
+        <v>97506</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135187656</v>
       </c>
       <c r="B5" t="n">
-        <v>97479</v>
+        <v>97506</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135187669</v>
       </c>
       <c r="B6" t="n">
-        <v>97479</v>
+        <v>97506</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135187620</v>
       </c>
       <c r="B7" t="n">
-        <v>79443</v>
+        <v>79470</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>135187617</v>
       </c>
       <c r="B8" t="n">
-        <v>83390</v>
+        <v>83417</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>135187648</v>
       </c>
       <c r="B9" t="n">
-        <v>83390</v>
+        <v>83417</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>135187662</v>
       </c>
       <c r="B10" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>135187668</v>
       </c>
       <c r="B11" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>135187637</v>
       </c>
       <c r="B12" t="n">
-        <v>92030</v>
+        <v>92057</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>135187635</v>
       </c>
       <c r="B13" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>135187640</v>
       </c>
       <c r="B14" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>135187643</v>
       </c>
       <c r="B15" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>135187591</v>
       </c>
       <c r="B16" t="n">
-        <v>91979</v>
+        <v>92006</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
         <v>135187586</v>
       </c>
       <c r="B17" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2480,7 +2480,7 @@
         <v>135187590</v>
       </c>
       <c r="B18" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>135187592</v>
       </c>
       <c r="B19" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2704,7 +2704,7 @@
         <v>135187600</v>
       </c>
       <c r="B20" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
         <v>135187605</v>
       </c>
       <c r="B21" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2928,7 +2928,7 @@
         <v>135187628</v>
       </c>
       <c r="B22" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
         <v>135187630</v>
       </c>
       <c r="B23" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         <v>135187632</v>
       </c>
       <c r="B24" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3264,7 +3264,7 @@
         <v>135187633</v>
       </c>
       <c r="B25" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3376,7 +3376,7 @@
         <v>135187638</v>
       </c>
       <c r="B26" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3488,7 +3488,7 @@
         <v>135187644</v>
       </c>
       <c r="B27" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3600,7 +3600,7 @@
         <v>135187650</v>
       </c>
       <c r="B28" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3712,7 +3712,7 @@
         <v>135187651</v>
       </c>
       <c r="B29" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3824,7 +3824,7 @@
         <v>135187659</v>
       </c>
       <c r="B30" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3936,7 +3936,7 @@
         <v>135187661</v>
       </c>
       <c r="B31" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4048,7 +4048,7 @@
         <v>135187663</v>
       </c>
       <c r="B32" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4160,7 +4160,7 @@
         <v>135187664</v>
       </c>
       <c r="B33" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
         <v>135187672</v>
       </c>
       <c r="B34" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4384,7 +4384,7 @@
         <v>135187675</v>
       </c>
       <c r="B35" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4496,7 +4496,7 @@
         <v>135187679</v>
       </c>
       <c r="B36" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4608,7 +4608,7 @@
         <v>135187589</v>
       </c>
       <c r="B37" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4720,7 +4720,7 @@
         <v>135187629</v>
       </c>
       <c r="B38" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4832,7 +4832,7 @@
         <v>135187616</v>
       </c>
       <c r="B39" t="n">
-        <v>79168</v>
+        <v>79195</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4944,7 +4944,7 @@
         <v>135187641</v>
       </c>
       <c r="B40" t="n">
-        <v>79168</v>
+        <v>79195</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5056,7 +5056,7 @@
         <v>135187613</v>
       </c>
       <c r="B41" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5168,7 +5168,7 @@
         <v>135187615</v>
       </c>
       <c r="B42" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5280,7 +5280,7 @@
         <v>135187606</v>
       </c>
       <c r="B43" t="n">
-        <v>80526</v>
+        <v>80553</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5392,7 +5392,7 @@
         <v>135187607</v>
       </c>
       <c r="B44" t="n">
-        <v>80526</v>
+        <v>80553</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5504,7 +5504,7 @@
         <v>135187610</v>
       </c>
       <c r="B45" t="n">
-        <v>80526</v>
+        <v>80553</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5616,7 +5616,7 @@
         <v>135187611</v>
       </c>
       <c r="B46" t="n">
-        <v>80526</v>
+        <v>80553</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5728,7 +5728,7 @@
         <v>135187619</v>
       </c>
       <c r="B47" t="n">
-        <v>80526</v>
+        <v>80553</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5840,7 +5840,7 @@
         <v>135187621</v>
       </c>
       <c r="B48" t="n">
-        <v>80526</v>
+        <v>80553</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5952,7 +5952,7 @@
         <v>135187622</v>
       </c>
       <c r="B49" t="n">
-        <v>80526</v>
+        <v>80553</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6064,7 +6064,7 @@
         <v>135187624</v>
       </c>
       <c r="B50" t="n">
-        <v>80526</v>
+        <v>80553</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6176,7 +6176,7 @@
         <v>135187626</v>
       </c>
       <c r="B51" t="n">
-        <v>80526</v>
+        <v>80553</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6288,7 +6288,7 @@
         <v>135187647</v>
       </c>
       <c r="B52" t="n">
-        <v>80526</v>
+        <v>80553</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6400,7 +6400,7 @@
         <v>135187677</v>
       </c>
       <c r="B53" t="n">
-        <v>80526</v>
+        <v>80553</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6512,7 +6512,7 @@
         <v>135187618</v>
       </c>
       <c r="B54" t="n">
-        <v>80530</v>
+        <v>80557</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6624,7 +6624,7 @@
         <v>135187596</v>
       </c>
       <c r="B55" t="n">
-        <v>80537</v>
+        <v>80564</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6736,7 +6736,7 @@
         <v>135187598</v>
       </c>
       <c r="B56" t="n">
-        <v>80537</v>
+        <v>80564</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6848,7 +6848,7 @@
         <v>135187678</v>
       </c>
       <c r="B57" t="n">
-        <v>80537</v>
+        <v>80564</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6960,7 +6960,7 @@
         <v>135187646</v>
       </c>
       <c r="B58" t="n">
-        <v>80538</v>
+        <v>80565</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7689,7 +7689,7 @@
         <v>135187595</v>
       </c>
       <c r="B64" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7806,7 +7806,7 @@
         <v>135187602</v>
       </c>
       <c r="B65" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7923,7 +7923,7 @@
         <v>135187603</v>
       </c>
       <c r="B66" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8040,7 +8040,7 @@
         <v>135187623</v>
       </c>
       <c r="B67" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8157,7 +8157,7 @@
         <v>135187645</v>
       </c>
       <c r="B68" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8274,7 +8274,7 @@
         <v>135187649</v>
       </c>
       <c r="B69" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8391,7 +8391,7 @@
         <v>135187654</v>
       </c>
       <c r="B70" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8508,7 +8508,7 @@
         <v>135187655</v>
       </c>
       <c r="B71" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8625,7 +8625,7 @@
         <v>135187658</v>
       </c>
       <c r="B72" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8742,7 +8742,7 @@
         <v>135187666</v>
       </c>
       <c r="B73" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8864,7 +8864,7 @@
         <v>135187670</v>
       </c>
       <c r="B74" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8981,7 +8981,7 @@
         <v>135187671</v>
       </c>
       <c r="B75" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9098,7 +9098,7 @@
         <v>135187588</v>
       </c>
       <c r="B76" t="n">
-        <v>79169</v>
+        <v>79196</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9210,7 +9210,7 @@
         <v>135187614</v>
       </c>
       <c r="B77" t="n">
-        <v>79169</v>
+        <v>79196</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9322,7 +9322,7 @@
         <v>135187642</v>
       </c>
       <c r="B78" t="n">
-        <v>79169</v>
+        <v>79196</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9434,7 +9434,7 @@
         <v>135187676</v>
       </c>
       <c r="B79" t="n">
-        <v>79169</v>
+        <v>79196</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9546,7 +9546,7 @@
         <v>135187593</v>
       </c>
       <c r="B80" t="n">
-        <v>80476</v>
+        <v>80503</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9658,7 +9658,7 @@
         <v>135187601</v>
       </c>
       <c r="B81" t="n">
-        <v>80476</v>
+        <v>80503</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9770,7 +9770,7 @@
         <v>135187608</v>
       </c>
       <c r="B82" t="n">
-        <v>80476</v>
+        <v>80503</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9882,7 +9882,7 @@
         <v>135187625</v>
       </c>
       <c r="B83" t="n">
-        <v>80476</v>
+        <v>80503</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9994,7 +9994,7 @@
         <v>135187627</v>
       </c>
       <c r="B84" t="n">
-        <v>80476</v>
+        <v>80503</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10106,7 +10106,7 @@
         <v>135187652</v>
       </c>
       <c r="B85" t="n">
-        <v>80476</v>
+        <v>80503</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
